--- a/output/pdf_financials_xlsx/ZONE.xlsx
+++ b/output/pdf_financials_xlsx/ZONE.xlsx
@@ -925,31 +925,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.727562</v>
+        <v>-0.727562</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.914746</v>
+        <v>-2.914746</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.879942</v>
+        <v>-1.879942</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.220489</v>
+        <v>-1.220489</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.934147</v>
+        <v>-1.934147</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2.062666</v>
+        <v>-2.062666</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.805646</v>
+        <v>-0.805646</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.891499</v>
+        <v>-0.891499</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.415738</v>
+        <v>-0.415738</v>
       </c>
     </row>
     <row r="17">
@@ -1097,31 +1097,31 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.727562</v>
+        <v>-0.727562</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.914746</v>
+        <v>-2.914746</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.879942</v>
+        <v>-1.879942</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.220489</v>
+        <v>-1.220489</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.934147</v>
+        <v>-1.934147</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2.062666</v>
+        <v>-2.062666</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.805646</v>
+        <v>-0.805646</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.891499</v>
+        <v>-0.891499</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.415738</v>
+        <v>-0.415738</v>
       </c>
     </row>
     <row r="21">
@@ -1199,31 +1199,31 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.727562</v>
+        <v>-0.727562</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.914746</v>
+        <v>-2.914746</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.879942</v>
+        <v>-1.879942</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.220489</v>
+        <v>-1.220489</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.934147</v>
+        <v>-1.934147</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2.062666</v>
+        <v>-2.062666</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.805646</v>
+        <v>-0.805646</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.891499</v>
+        <v>-0.891499</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.415738</v>
+        <v>-0.415738</v>
       </c>
     </row>
     <row r="24">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>41.639229</v>
+        <v>-41.639229</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>62.664733</v>
+        <v>-62.664733</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -1353,31 +1353,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.727562</v>
+        <v>-0.727562</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2.914746</v>
+        <v>-2.914746</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.879942</v>
+        <v>-1.879942</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.220489</v>
+        <v>-1.220489</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.934147</v>
+        <v>-1.934147</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2.062666</v>
+        <v>-2.062666</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.805646</v>
+        <v>-0.805646</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.891499</v>
+        <v>-0.891499</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.415738</v>
+        <v>-0.415738</v>
       </c>
     </row>
     <row r="28">
@@ -1421,31 +1421,31 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.727562</v>
+        <v>-0.727562</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.920777</v>
+        <v>-2.908715</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.882158</v>
+        <v>-1.877726</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.220489</v>
+        <v>-1.220489</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.934147</v>
+        <v>-1.934147</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.062666</v>
+        <v>-2.062666</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.805646</v>
+        <v>-0.805646</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.891499</v>
+        <v>-0.891499</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.415738</v>
+        <v>-0.415738</v>
       </c>
     </row>
     <row r="30">
@@ -1455,31 +1455,31 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>899.4239232556989</v>
+        <v>-899.4239232556989</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>7183.946183928967</v>
+        <v>-7154.278476031188</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>2410.365494454832</v>
+        <v>-2404.689701098788</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>3055.423707597947</v>
+        <v>-3055.423707597947</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>4730.585041334442</v>
+        <v>-4730.585041334442</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>5420.935611038108</v>
+        <v>-5420.935611038108</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>2051.973918801895</v>
+        <v>-2051.973918801895</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2416.968957570828</v>
+        <v>-2416.968957570828</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1987.940515468847</v>
+        <v>-1987.940515468847</v>
       </c>
     </row>
     <row r="31">
@@ -1489,31 +1489,31 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1523,31 +1523,31 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>899.4239232556989</v>
+        <v>-899.4239232556989</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>7169.112329980078</v>
+        <v>-7169.112329980078</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>2407.52759777681</v>
+        <v>-2407.52759777681</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>3055.423707597947</v>
+        <v>-3055.423707597947</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4730.585041334442</v>
+        <v>-4730.585041334442</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>5420.935611038108</v>
+        <v>-5420.935611038108</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>2051.973918801895</v>
+        <v>-2051.973918801895</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2416.968957570828</v>
+        <v>-2416.968957570828</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1987.940515468847</v>
+        <v>-1987.940515468847</v>
       </c>
     </row>
     <row r="33">
@@ -21375,16 +21375,16 @@
         </is>
       </c>
       <c r="J271" s="5" t="n">
-        <v>2.062666</v>
+        <v>-2.062666</v>
       </c>
       <c r="K271" s="5" t="n">
-        <v>0.805646</v>
+        <v>-0.805646</v>
       </c>
       <c r="L271" s="5" t="n">
-        <v>0.891499</v>
+        <v>-0.891499</v>
       </c>
       <c r="M271" s="5" t="n">
-        <v>0.415738</v>
+        <v>-0.415738</v>
       </c>
     </row>
     <row r="272">
@@ -22869,10 +22869,10 @@
         </is>
       </c>
       <c r="I296" s="5" t="n">
-        <v>1.934147</v>
+        <v>-1.934147</v>
       </c>
       <c r="J296" s="5" t="n">
-        <v>2.062666</v>
+        <v>-2.062666</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
@@ -23684,16 +23684,16 @@
         </is>
       </c>
       <c r="F310" s="5" t="n">
-        <v>2.914746</v>
+        <v>-2.914746</v>
       </c>
       <c r="G310" s="5" t="n">
-        <v>1.879942</v>
+        <v>-1.879942</v>
       </c>
       <c r="H310" s="5" t="n">
-        <v>1.220489</v>
+        <v>-1.220489</v>
       </c>
       <c r="I310" s="5" t="n">
-        <v>1.934147</v>
+        <v>-1.934147</v>
       </c>
       <c r="J310" t="inlineStr">
         <is>
@@ -25239,10 +25239,10 @@
         </is>
       </c>
       <c r="E336" s="5" t="n">
-        <v>0.727562</v>
+        <v>-0.727562</v>
       </c>
       <c r="F336" s="5" t="n">
-        <v>2.914746</v>
+        <v>-2.914746</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ZONE.xlsx
+++ b/output/pdf_financials_xlsx/ZONE.xlsx
@@ -1570,25 +1570,25 @@
         <v>0.93265</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.011722</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.149494</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.088207</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.176884</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.003342</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.0007159999999999999</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.185805</v>
       </c>
     </row>
     <row r="35">
@@ -1638,25 +1638,25 @@
         <v>0.93265</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.011722</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.149494</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.088207</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.176884</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.003342</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.0007159999999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.185805</v>
       </c>
     </row>
     <row r="37">
@@ -2046,19 +2046,19 @@
         <v>0.270254</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.050685</v>
+        <v>0.038963</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.164812</v>
+        <v>0.015318</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.132411</v>
+        <v>0.044204</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.231552</v>
+        <v>0.054668</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.039509</v>
+        <v>0.036167</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -23150,7 +23150,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -23909,7 +23909,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -24273,7 +24273,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">

--- a/output/pdf_financials_xlsx/ZONE.xlsx
+++ b/output/pdf_financials_xlsx/ZONE.xlsx
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.008126</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0.006031</v>
@@ -1396,10 +1396,10 @@
         <v>0.002216</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.002077</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.006933</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0</v>
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.727562</v>
+        <v>-0.719436</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-2.908715</v>
@@ -1430,10 +1430,10 @@
         <v>-1.877726</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.220489</v>
+        <v>-1.218412</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.934147</v>
+        <v>-1.927214</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-2.062666</v>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-899.4239232556989</v>
+        <v>-889.3784304999258</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>-7154.278476031188</v>
@@ -1464,10 +1464,10 @@
         <v>-2404.689701098788</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-3055.423707597947</v>
+        <v>-3050.22405807986</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-4730.585041334442</v>
+        <v>-4713.628136770533</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-5420.935611038108</v>
@@ -3849,19 +3849,19 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.008126</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.006031</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.002216</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.002077</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.006933</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
@@ -13665,7 +13665,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -18805,7 +18809,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E228" s="5" t="n">
         <v>0.008126</v>
       </c>
@@ -23439,7 +23447,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -24873,7 +24885,11 @@
           <t>Depreciation of property and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E330" s="5" t="n">
         <v>0.008126</v>
       </c>

--- a/output/pdf_financials_xlsx/ZONE.xlsx
+++ b/output/pdf_financials_xlsx/ZONE.xlsx
@@ -2725,22 +2725,22 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.230767</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.184808</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.253101</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.151201</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.205598</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.102231</v>
       </c>
     </row>
     <row r="68">
@@ -2759,22 +2759,22 @@
         <v>0.504497</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.370629</v>
+        <v>0.601396</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.225341</v>
+        <v>0.410149</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.5547609999999999</v>
+        <v>0.807862</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.612546</v>
+        <v>0.763747</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.736842</v>
+        <v>0.9424400000000001</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.486942</v>
+        <v>0.5891729999999999</v>
       </c>
     </row>
     <row r="69">
@@ -2997,22 +2997,22 @@
         <v>0.755975</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.759313</v>
+        <v>0.528546</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.571415</v>
+        <v>0.386607</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.592276</v>
+        <v>0.339175</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.450091</v>
+        <v>0.29889</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.682947</v>
+        <v>0.477349</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.809854</v>
+        <v>0.707623</v>
       </c>
     </row>
     <row r="76">
@@ -10055,7 +10055,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
